--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115106196</v>
+        <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99142</v>
+        <v>99355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,54 +1042,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Erik-Bengtsstugan, Jmt</t>
+          <t>Svanamyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504854</v>
+        <v>504864</v>
       </c>
       <c r="R5" t="n">
-        <v>7007976</v>
+        <v>7007974</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,17 +1104,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 1 st stjälk av tvåblad på en delvis igenväxt gräsmark med spår av tidigare hävd. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7698-2024.</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,40 +1122,34 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Frisk gräsmark med lövträd</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>En äldre delvis igenväxt infartsväg med fältskikt dominerat av gräs och örter med spår av tidigare hävd med flertalet hävdgynnade arter. Trädskikt av asp, tall, sälg och björk. På frisk mark enligt markfuktighetsdata.</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115106196</t>
+          <t>https://artportalen.se/Sighting/136949689</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118432636</v>
+        <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99142</v>
+        <v>99355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,37 +1157,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Erik-Bengtsstugan, Jmt</t>
+          <t>Svanamyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504861</v>
+        <v>504879</v>
       </c>
       <c r="R6" t="n">
-        <v>7007922</v>
+        <v>7008034</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,12 +1219,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Förekommer glest längs sträckan</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,71 +1238,96 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tobias Nykänen</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tobias Nykänen</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118432636</t>
+          <t>https://artportalen.se/Sighting/136950007</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123451229</v>
+        <v>115106196</v>
       </c>
       <c r="B7" t="n">
-        <v>102464</v>
+        <v>99142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221343</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarttjärnen, 975 m N om i vägkanter på väg 744, Jmt</t>
+          <t>Erik-Bengtsstugan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504897</v>
+        <v>504854</v>
       </c>
       <c r="R7" t="n">
-        <v>7008131</v>
+        <v>7007976</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,17 +1351,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1993-06-24</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1993-06-24</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikstaxruta 19F2c13</t>
+          <t>Minst 1 st stjälk av tvåblad på en delvis igenväxt gräsmark med spår av tidigare hävd. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7698-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,71 +1370,82 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Frisk gräsmark med lövträd</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>En äldre delvis igenväxt infartsväg med fältskikt dominerat av gräs och örter med spår av tidigare hävd med flertalet hävdgynnade arter. Trädskikt av asp, tall, sälg och björk. På frisk mark enligt markfuktighetsdata.</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123451229</t>
+          <t>https://artportalen.se/Sighting/115106196</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123451254</v>
+        <v>118432636</v>
       </c>
       <c r="B8" t="n">
-        <v>98050</v>
+        <v>99142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222112</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnen, 975 m N om i vägkanter på väg 744, Jmt</t>
+          <t>Erik-Bengtsstugan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504897</v>
+        <v>504861</v>
       </c>
       <c r="R8" t="n">
-        <v>7008131</v>
+        <v>7007922</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1443,17 +1469,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1993-06-24</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1993-06-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikstaxruta 19F2c13</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,16 +1489,456 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Tobias Nykänen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Tobias Nykänen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118432636</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136949688</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svanamyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>504879</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7008053</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136949688</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136949690</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svanamyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>504892</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7007979</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136949690</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123451229</v>
+      </c>
+      <c r="B11" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svarttjärnen, 975 m N om i vägkanter på väg 744, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>504897</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7008131</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1993-06-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1993-06-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19F2c13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123451229</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123451254</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svarttjärnen, 975 m N om i vägkanter på väg 744, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>504897</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7008131</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>1993-06-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1993-06-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19F2c13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/123451254</t>
         </is>
@@ -1492,6 +1953,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136949689</v>
       </c>
       <c r="B5" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136950007</v>
       </c>
       <c r="B6" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136949688</v>
       </c>
       <c r="B9" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136949690</v>
       </c>
       <c r="B10" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
